--- a/public/templates/booking-import-template.xlsx
+++ b/public/templates/booking-import-template.xlsx
@@ -64,8 +64,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,25 +400,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N12"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" customWidth="1"/>
-    <col min="13" max="13" width="10.83203125" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>5/10/2026</v>
+      <c r="A1" s="1" t="str">
+        <v>5 Oct 26</v>
       </c>
       <c r="B1" t="str">
         <v/>
@@ -504,8 +505,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>5/10/2026</v>
+      <c r="A3" s="1" t="str">
+        <v>5 Oct 26</v>
       </c>
       <c r="B3" t="str">
         <v>PP</v>
@@ -548,8 +549,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>5/10/2026</v>
+      <c r="A4" s="1" t="str">
+        <v>6 Oct 26</v>
       </c>
       <c r="B4" t="str">
         <v>James Bond</v>

--- a/public/templates/booking-import-template.xlsx
+++ b/public/templates/booking-import-template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:O12"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -414,6 +414,7 @@
     <col min="12" max="12" width="12.83203125" customWidth="1"/>
     <col min="13" max="13" width="12.83203125" customWidth="1"/>
     <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -459,6 +460,9 @@
       <c r="N1" t="str">
         <v/>
       </c>
+      <c r="O1" t="str">
+        <v/>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -492,7 +496,7 @@
         <v>COT</v>
       </c>
       <c r="K2" t="str">
-        <v>Remark</v>
+        <v>Park Fee</v>
       </c>
       <c r="L2" t="str">
         <v>Pick Up</v>
@@ -502,6 +506,9 @@
       </c>
       <c r="N2" t="str">
         <v>VAN</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Remark</v>
       </c>
     </row>
     <row r="3">
@@ -536,7 +543,7 @@
         <v>800</v>
       </c>
       <c r="K3" t="str">
-        <v>Excluding National Park Fee</v>
+        <v>EXC</v>
       </c>
       <c r="L3" t="str">
         <v>08:00</v>
@@ -546,6 +553,9 @@
       </c>
       <c r="N3" t="str">
         <v/>
+      </c>
+      <c r="O3" t="str">
+        <v>Arrive 10 min early</v>
       </c>
     </row>
     <row r="4">
@@ -580,7 +590,7 @@
         <v/>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>INC</v>
       </c>
       <c r="L4" t="str">
         <v>07:30</v>
@@ -591,6 +601,9 @@
       <c r="N4" t="str">
         <v/>
       </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -635,6 +648,9 @@
       <c r="N5" t="str">
         <v/>
       </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -679,6 +695,9 @@
       <c r="N6" t="str">
         <v/>
       </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -723,6 +742,9 @@
       <c r="N7" t="str">
         <v/>
       </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -767,6 +789,9 @@
       <c r="N8" t="str">
         <v/>
       </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -811,6 +836,9 @@
       <c r="N9" t="str">
         <v/>
       </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -855,6 +883,9 @@
       <c r="N10" t="str">
         <v/>
       </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -899,6 +930,9 @@
       <c r="N11" t="str">
         <v/>
       </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -943,10 +977,13 @@
       <c r="N12" t="str">
         <v/>
       </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O12"/>
   </ignoredErrors>
 </worksheet>
 </file>